--- a/internal_doc/05.测试设计/OM/om-exception-test.xlsx
+++ b/internal_doc/05.测试设计/OM/om-exception-test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="关注点" sheetId="1" r:id="rId1"/>
@@ -528,10 +528,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>会全新安装。安装后版本，安装路径，进程用户，sdbcm端口号都是最新的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>不能出现死锁，和有机器没被安装上的情况。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -633,6 +629,10 @@
   </si>
   <si>
     <t>使用add host的场景8，删除机器时，强杀OM Svc,OM Svc能够重启，起来后能继续进行任务，并成功完成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会全新安装。安装后版本，安装路径，进程用户，sdbcm端口号都是最新的。另外，目标机器/etc/default/sequoiadb文件也要求有最新的结果。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -705,13 +705,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -721,6 +715,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1093,42 +1093,42 @@
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="1" t="s">
@@ -1197,110 +1197,110 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="35.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="42.875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="21.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.625" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="35.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="42.875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" ht="45.75" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="45.75" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="27">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1319,198 +1319,198 @@
   <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="43.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="43.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="25" style="3" customWidth="1"/>
-    <col min="4" max="4" width="19.25" style="3" customWidth="1"/>
-    <col min="5" max="5" width="25.625" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="43.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="43.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.625" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" ht="291" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="291" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="40.5">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="40.5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="27">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="27">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="27">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="40.5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="81">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19" spans="1:5" ht="40.5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="40.5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="4" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="40.5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1529,158 +1529,158 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="46.625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="28.625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="19.625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="19.75" style="3" customWidth="1"/>
-    <col min="5" max="5" width="19" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="46.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="19.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" ht="275.25" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="275.25" customHeight="1">
+      <c r="A1" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="40.5">
+      <c r="A4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="54">
+      <c r="A5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="40.5">
+      <c r="A6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="67.5">
+      <c r="A7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="54">
+      <c r="A10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="27">
+      <c r="A11" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="27">
+      <c r="A12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="40.5">
-      <c r="A4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="54">
-      <c r="A5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="40.5">
-      <c r="A6" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="40.5">
-      <c r="A7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="6" t="s">
+    <row r="15" spans="1:5" ht="27">
+      <c r="A15" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="5"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="5"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="4" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="54">
-      <c r="A10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="27">
-      <c r="A11" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="27">
-      <c r="A12" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="27">
-      <c r="A15" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="7"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="7"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
     <row r="20" spans="1:2" ht="27">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="27">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="27">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="27">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1699,68 +1699,68 @@
   <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="42.125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="36.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="21.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16.375" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="42.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="36.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="30.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.375" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" ht="121.5" customHeight="1">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="121.5" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="6" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="3" t="s">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="40.5">
+      <c r="A13" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="40.5">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="14" spans="1:5" ht="40.5">
+      <c r="A14" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="40.5">
-      <c r="A14" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>118</v>
+      <c r="B14" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1778,28 +1778,28 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="33.375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.25" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="33.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="24" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.25" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1814,28 +1814,28 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="30.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="28.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="33.375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="18.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="30.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="28.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="33.375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>33</v>
       </c>
     </row>

--- a/internal_doc/05.测试设计/OM/om-exception-test.xlsx
+++ b/internal_doc/05.测试设计/OM/om-exception-test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="关注点" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="151">
   <si>
     <t>操作系统</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -635,12 +635,154 @@
     <t>会全新安装。安装后版本，安装路径，进程用户，sdbcm端口号都是最新的。另外，目标机器/etc/default/sequoiadb文件也要求有最新的结果。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>在集群环境下，若开启了鉴权，是否能顺利完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以安装在控制机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以安装非控制机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制机的sdbcm.conf文件中找不到目标机器的OM Agent端口号时，能够准确报错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要准确报错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常场景：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通场景：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在集群环境下，若开启了鉴权，在填写鉴权密码错误的情况下，能否删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉴权相关：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当standalone还有数据的时候，能否删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能。执行删除将失败。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>那些没有数据的组可以被删除，但是有数据的组在删除时将报错，导致整个任务失败。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景10：当集群还有数据的时候，能否删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当删除standalone进行到一半时，强杀sdbcm，让sdbcm重启。Sdbcm是否能重新删除业务并成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当删除集群进行到一半时，强杀sdbcm，让sdbcm重启。Sdbcm是否能重新删除业务并成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程/线程相关：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当删除standalone进行到一半时，强杀sdbom，让sdbom重启。Sdbcm能否继续删除业务并成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场景10的条件下，当删除所有数据（表空间）之后，能否继续进行业务删除。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">add business
+添加业务是个后台任务。目前（1.12）业务类型只有SequoiaDB。安装SequoiaDB业务可选择安装单机或集群版。两者的安装步骤差别比较大。
+一、添加单机
+1.使用root权限ssh到目标机器。
+2.从根据目标机器的hostname,从控制机的sdbcm.conf文件中获取目标机器的OM Agent端口。
+3.尝试从目标机器上删除端口号相同的，并且拥有指定cluster,business,user tag的standalone。
+4.修改数据安装目录的属组为将要安装的进程用户组（例如：sdbadmin:sdbadmin_group）。
+5.安装standalone到目标机器。
+安装standalone是直连目标机器的OM Agent，利用它来创建standalone的。
+二、添加集群
+1.先创建一个临时的coord。
+2.连上临时coord,创建catalog组，并添加catalog节点。（串行）
+3.连上临时coord,创建coord组，并添加coord节点。（串行）
+4.连上临时coord,创建data组，并添加该组的节点。（一个组一个线程，最多10个线程。每一线程安装完当前组之后，继续取下一还没安装的组来安装，直到没有组可以安装后，线程退出）。
+（5.回滚）
+6.删除临时coord。
+当2-4任一步骤失败，程序跳转到回滚操作。回滚的顺序为先删除所有数据组，然后再删coord组，最后删除catalog组。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.不会死锁；2.所有数据组都被安装，说明有些线程至少能安装两个或以上的数据组。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景7：安装15个数据组，每个数据组三个节点（或者两个）。1.测试多线程并发是否会出现死锁；2.测试10个线程中其中一些线程是否会安装两个或两个以上的数据组；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装业务在控制机和非控制机的混搭环境。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场景7的条件下，强制杀掉sdbcm，sdbcm重启后，是否能重新安装并完成任务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场景7的条件下，强制杀掉sdbom,sdbom重启后，sdbcm能否继续安装，并完成任务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当standalone没有数据的时候，能否删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove business
+在数据库没有数据的情况上，删除通过OM添加的业务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -680,6 +822,23 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -701,7 +860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -721,6 +880,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1696,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="42.125" style="2" customWidth="1"/>
@@ -1742,24 +1907,24 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="40.5">
-      <c r="A13" s="2" t="s">
+    <row r="16" spans="1:5" ht="40.5">
+      <c r="A16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="40.5">
-      <c r="A14" s="2" t="s">
+    <row r="17" spans="1:2" ht="40.5">
+      <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1775,10 +1940,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="33.375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="45.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="30.375" style="2" customWidth="1"/>
     <col min="3" max="3" width="26.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="24" style="2" customWidth="1"/>
@@ -1786,35 +1951,130 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="296.25" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="27">
+      <c r="A8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="54">
+      <c r="A20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="27">
+      <c r="A26" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="27">
+      <c r="A27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:XFD1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="30.875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="49.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="28.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="33.375" style="2" customWidth="1"/>
     <col min="4" max="4" width="18.875" style="2" customWidth="1"/>
@@ -1822,24 +2082,147 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="113.25" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="27">
+      <c r="A11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="27">
+      <c r="A12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="40.5">
+      <c r="A17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="27">
+      <c r="A18" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="27">
+      <c r="A30" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="27">
+      <c r="A31" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="27">
+      <c r="A36" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="27">
+      <c r="A37" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:XFD1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/internal_doc/05.测试设计/OM/om-exception-test.xlsx
+++ b/internal_doc/05.测试设计/OM/om-exception-test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="关注点" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="181">
   <si>
     <t>操作系统</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -358,7 +358,199 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>开启防火墙，scanhost能否成功</t>
+    <t>1.12可以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忽略错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无残留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当一台或多台目标机器的/tmp目录空间不足时，是否能准确地报错，并停止执行后面的checkhost和post-check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add host添加控制机，进程用户（如：sdbadmin用户），进程用户组，进程用户密码，安装路径，sdbcm端口号都一致，是否能够安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要准确报错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标机器的/tmp/omatmp空间不够，传送安装包将失败，失败后，能否准确报错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标机器安装SequoiaDB Run包时，磁盘空间不够而导致失败，能否准确报错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加机器失败后，是否会对目标机器执行一次uninstall操作，删除安装过的东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失败后，需要卸载已安装的东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加机器结束后，不管成功失败，/tmp/omatmp目录的临时文件是否被删除（日志文件除外）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要清除这些临时的东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add host时，当目标机器已经安装SequoiaDB，但在它的版本，安装路径，进程用户，sdbcm端口号中，有一项或多项和将要安装的信息不符合时，是否会覆盖安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add host时，当目标机器已经安装有版本、安装路径、进程用户、sdbcm端口号都相同的SequoiaDB时，是否会覆盖安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>add host添加控制机，进程用户（如：sdbadmin用户），进程用户组，进程用户密码，安装路径，sdbcm端口号这几项中，一项或几项和原来安装的不符合，是否会报错，并停止安装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能安装，并且会准确报告那一项和原来的不符合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不会覆盖安装，在安装进度中可以看到机器时很快就安装完成的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以安装,并且不会覆盖安装，在安装进度中可以看到机器时很快就安装完成的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能出现死锁，和有机器没被安装上的情况。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OM Agent在退出之前，应该要告知OM Svc Task 失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景8：添加机器时多线程执行的，最多10个线程。每个线程添加完一台机器的时候，会继续取下一台机器添加。超过10台机器，进程安装，看看是否会出现死锁，或有机器没被安装上的情况。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场景8条件下，正常杀掉和强杀OM Agent进程，web是否会停止任务并报错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场景8条件下，让OM Svc停止运行一段时间，然后重启它，要求web和OM Agent能继续正常工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>web 和 OM Agent都能继续正常工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程/线程相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>磁盘相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>网络相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标机器开启防火墙后，添加主机是否能成功。因为控制机需要传输安装包到目标机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">remove host
+删除机器是个后台的task任务。
+OM Agent取到task信息后，开始执行删除机器操作。删除机器时单线程操作，一台一台删。在删除过程会不断把进度更新到OM Svc。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">删除机器主要流程：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1.使用root权限ssh到目标机器。
+2.判断目标机器是否为控制机，若是控制机，则停止删除，并返回成功。控制机是不能通过OM删除的，必须手动删除。
+3.判断目标机器是否已被删除，若是，直接返回成功
+4.删除目标机器</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一般场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除控制机，是否能直接完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接跳过完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用add host的场景8，删除机器时，强杀OM Agent,OM Agent能够重启，起来后能继续进行任务，并成功完成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功删除所有机器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用add host的场景8，删除机器时，强杀OM Svc,OM Svc能够重启，起来后能继续进行任务，并成功完成。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会全新安装。安装后版本，安装路径，进程用户，sdbcm端口号都是最新的。另外，目标机器/etc/default/sequoiadb文件也要求有最新的结果。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在集群环境下，若开启了鉴权，是否能顺利完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可以安装在控制机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -366,27 +558,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.12可以</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>忽略错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无残留</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当一台或多台目标机器的/tmp目录空间不足时，是否能准确地报错，并停止执行后面的checkhost和post-check</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以安装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add host添加控制机，进程用户（如：sdbadmin用户），进程用户组，进程用户密码，安装路径，sdbcm端口号都一致，是否能够安装</t>
+    <t>是否可以安装非控制机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制机的sdbcm.conf文件中找不到目标机器的OM Agent端口号时，能够准确报错</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -394,35 +570,201 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>目标机器的/tmp/omatmp空间不够，传送安装包将失败，失败后，能否准确报错</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标机器安装SequoiaDB Run包时，磁盘空间不够而导致失败，能否准确报错</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加机器失败后，是否会对目标机器执行一次uninstall操作，删除安装过的东西</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>失败后，需要卸载已安装的东西</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>添加机器结束后，不管成功失败，/tmp/omatmp目录的临时文件是否被删除（日志文件除外）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要清除这些临时的东西</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add host时，当目标机器已经安装SequoiaDB，但在它的版本，安装路径，进程用户，sdbcm端口号中，有一项或多项和将要安装的信息不符合时，是否会覆盖安装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>add host时，当目标机器已经安装有版本、安装路径、进程用户、sdbcm端口号都相同的SequoiaDB时，是否会覆盖安装</t>
+    <t>集群</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通场景：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在集群环境下，若开启了鉴权，在填写鉴权密码错误的情况下，能否删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鉴权相关：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当standalone还有数据的时候，能否删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能。执行删除将失败。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>那些没有数据的组可以被删除，但是有数据的组在删除时将报错，导致整个任务失败。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景10：当集群还有数据的时候，能否删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当删除集群进行到一半时，强杀sdbcm，让sdbcm重启。Sdbcm是否能重新删除业务并成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程/线程相关：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当删除standalone进行到一半时，强杀sdbom，让sdbom重启。Sdbcm能否继续删除业务并成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场景10的条件下，当删除所有数据（表空间）之后，能否继续进行业务删除。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">add business
+添加业务是个后台任务。目前（1.12）业务类型只有SequoiaDB。安装SequoiaDB业务可选择安装单机或集群版。两者的安装步骤差别比较大。
+一、添加单机
+1.使用root权限ssh到目标机器。
+2.从根据目标机器的hostname,从控制机的sdbcm.conf文件中获取目标机器的OM Agent端口。
+3.尝试从目标机器上删除端口号相同的，并且拥有指定cluster,business,user tag的standalone。
+4.修改数据安装目录的属组为将要安装的进程用户组（例如：sdbadmin:sdbadmin_group）。
+5.安装standalone到目标机器。
+安装standalone是直连目标机器的OM Agent，利用它来创建standalone的。
+二、添加集群
+1.先创建一个临时的coord。
+2.连上临时coord,创建catalog组，并添加catalog节点。（串行）
+3.连上临时coord,创建coord组，并添加coord节点。（串行）
+4.连上临时coord,创建data组，并添加该组的节点。（一个组一个线程，最多10个线程。每一线程安装完当前组之后，继续取下一还没安装的组来安装，直到没有组可以安装后，线程退出）。
+（5.回滚）
+6.删除临时coord。
+当2-4任一步骤失败，程序跳转到回滚操作。回滚的顺序为先删除所有数据组，然后再删coord组，最后删除catalog组。
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.不会死锁；2.所有数据组都被安装，说明有些线程至少能安装两个或以上的数据组。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景7：安装15个数据组，每个数据组三个节点（或者两个）。1.测试多线程并发是否会出现死锁；2.测试10个线程中其中一些线程是否会安装两个或两个以上的数据组；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安装业务在控制机和非控制机的混搭环境。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场景7的条件下，强制杀掉sdbcm，sdbcm重启后，是否能重新安装并完成任务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在场景7的条件下，强制杀掉sdbom,sdbom重启后，sdbcm能否继续安装，并完成任务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当standalone没有数据的时候，能否删除业务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>remove business
+在数据库没有数据的情况上，删除通过OM添加的业务。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误的hostname或ip不能连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有两个结果，它们的ip地址相同，但hostname不一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>web端做了处理，只能随机选择一个显示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不OK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能够扫描成功。存在隐患。比如将rhel64-test8 映射到 192.168.20.165和192.168.20.166，在机器上ping rhel64-test8，发现它的地址为192.168.20.166,但在web上扫描，发现它的地址为192.168.20.165</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能ping,但ssh失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>还没测</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制机防火墙关闭，远端机器的防火墙开启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制机防火墙关闭，远端机器的防火墙关闭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制机防火墙开启（需要让8000能够开发给web来连接），远端机器的防火墙开启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制机防火墙开启（需要让8000能够开发给web来连接），远端机器的防火墙关闭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标机器防火墙开启</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防火墙相关</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失败。因为一旦防火墙关闭，OM Svc 在checkhost阶段就不能把消息发送到目标机器的OM Agent。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>失败，报了个network error</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标机器防火墙开启，但是开放一些临时OM Agentke可能使用到的端口。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没测完</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能安装，并准确报错</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不会覆盖安装，如果目标机器的sdbcm没有启动，它将被拉起。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>会覆盖安装，原来的东西将保留下来。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -507,204 +849,36 @@
 a.使用root权限连接到目标机器。
 b.判断目标机器是否为控制机，若是，停止下面的步骤直接返回。
 c.在目标机器的/tmp/omatmp目下建立临时目录
-把安装run包和一些脚本</t>
+把安装run包和一些脚本传送到这个临时目录</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>add host添加控制机，进程用户（如：sdbadmin用户），进程用户组，进程用户密码，安装路径，sdbcm端口号这几项中，一项或几项和原来安装的不符合，是否会报错，并停止安装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不能安装，并且会准确报告那一项和原来的不符合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不会覆盖安装，在安装进度中可以看到机器时很快就安装完成的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以安装,并且不会覆盖安装，在安装进度中可以看到机器时很快就安装完成的。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不能出现死锁，和有机器没被安装上的情况。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OM Agent在退出之前，应该要告知OM Svc Task 失败</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景8：添加机器时多线程执行的，最多10个线程。每个线程添加完一台机器的时候，会继续取下一台机器添加。超过10台机器，进程安装，看看是否会出现死锁，或有机器没被安装上的情况。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在场景8条件下，正常杀掉和强杀OM Agent进程，web是否会停止任务并报错</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在场景8条件下，让OM Svc停止运行一段时间，然后重启它，要求web和OM Agent能继续正常工作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>web 和 OM Agent都能继续正常工作</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程/线程相关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>磁盘相关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络相关</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标机器开启防火墙后，添加主机是否能成功。因为控制机需要传输安装包到目标机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">remove host
-删除机器是个后台的task任务。
-OM Agent取到task信息后，开始执行删除机器操作。删除机器时单线程操作，一台一台删。在删除过程会不断把进度更新到OM Svc。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">删除机器主要流程：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1.使用root权限ssh到目标机器。
-2.判断目标机器是否为控制机，若是控制机，则停止删除，并返回成功。控制机是不能通过OM删除的，必须手动删除。
-3.判断目标机器是否已被删除，若是，直接返回成功
-4.删除目标机器</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一般场景</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>删除控制机，是否能直接完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直接跳过完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用add host的场景8，删除机器时，强杀OM Agent,OM Agent能够重启，起来后能继续进行任务，并成功完成。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成功删除所有机器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用add host的场景8，删除机器时，强杀OM Svc,OM Svc能够重启，起来后能继续进行任务，并成功完成。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>会全新安装。安装后版本，安装路径，进程用户，sdbcm端口号都是最新的。另外，目标机器/etc/default/sequoiadb文件也要求有最新的结果。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在集群环境下，若开启了鉴权，是否能顺利完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否可以安装在控制机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否可以安装非控制机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>控制机的sdbcm.conf文件中找不到目标机器的OM Agent端口号时，能够准确报错</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要准确报错</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集群</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>异常场景：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>普通场景：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在集群环境下，若开启了鉴权，在填写鉴权密码错误的情况下，能否删除业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不可以</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鉴权相关：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当standalone还有数据的时候，能否删除业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不能。执行删除将失败。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>那些没有数据的组可以被删除，但是有数据的组在删除时将报错，导致整个任务失败。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景10：当集群还有数据的时候，能否删除业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>可以。</t>
+    <t>若控制机开启了ssh的端口，addhost是成功的。但是，开启防火墙后，可能会对后续安装业务照成影响。应该后续需要连接到目标机器的OM Agent，如果OM Agent 的端口没有开放，则在添加完该机器之后，会在主页上显示，改机器出现故障。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>符合预期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在安装过程，强杀控制机的sdbcm。控制机的sdbcm重启后，能否重新执行，并成功完成安装。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在安装过程，强杀控制机的sdbom。控制机的sdbom重启后，sdbcm能否继续执行，并成功完成安装。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>也可以删除，不符合预期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>进程线程相关：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>当删除standalone进行到一半时，强杀sdbom，让sdbom重启。Sdbcm是否能继续删除业务并成功</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -712,69 +886,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>当删除集群进行到一半时，强杀sdbcm，让sdbcm重启。Sdbcm是否能重新删除业务并成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>进程/线程相关：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当删除standalone进行到一半时，强杀sdbom，让sdbom重启。Sdbcm能否继续删除业务并成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在场景10的条件下，当删除所有数据（表空间）之后，能否继续进行业务删除。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">add business
-添加业务是个后台任务。目前（1.12）业务类型只有SequoiaDB。安装SequoiaDB业务可选择安装单机或集群版。两者的安装步骤差别比较大。
-一、添加单机
-1.使用root权限ssh到目标机器。
-2.从根据目标机器的hostname,从控制机的sdbcm.conf文件中获取目标机器的OM Agent端口。
-3.尝试从目标机器上删除端口号相同的，并且拥有指定cluster,business,user tag的standalone。
-4.修改数据安装目录的属组为将要安装的进程用户组（例如：sdbadmin:sdbadmin_group）。
-5.安装standalone到目标机器。
-安装standalone是直连目标机器的OM Agent，利用它来创建standalone的。
-二、添加集群
-1.先创建一个临时的coord。
-2.连上临时coord,创建catalog组，并添加catalog节点。（串行）
-3.连上临时coord,创建coord组，并添加coord节点。（串行）
-4.连上临时coord,创建data组，并添加该组的节点。（一个组一个线程，最多10个线程。每一线程安装完当前组之后，继续取下一还没安装的组来安装，直到没有组可以安装后，线程退出）。
-（5.回滚）
-6.删除临时coord。
-当2-4任一步骤失败，程序跳转到回滚操作。回滚的顺序为先删除所有数据组，然后再删coord组，最后删除catalog组。
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1.不会死锁；2.所有数据组都被安装，说明有些线程至少能安装两个或以上的数据组。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景7：安装15个数据组，每个数据组三个节点（或者两个）。1.测试多线程并发是否会出现死锁；2.测试10个线程中其中一些线程是否会安装两个或两个以上的数据组；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安装业务在控制机和非控制机的混搭环境。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在场景7的条件下，强制杀掉sdbcm，sdbcm重启后，是否能重新安装并完成任务。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在场景7的条件下，强制杀掉sdbom,sdbom重启后，sdbcm能否继续安装，并完成任务。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>当standalone没有数据的时候，能否删除业务</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>remove business
-在数据库没有数据的情况上，删除通过OM添加的业务。</t>
+    <t>当删除standalone进行到一半时，停止sdbom，然后让sdbom重启。Sdbcm是否能继续删除业务并成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>符合预期。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在安装过程，停止sdbom5分钟(只要从目标机器看到standalone已成功安装就行)，然后重启sdbom,sdbcm能否继续执行，并成功完成安装。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -875,17 +995,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1258,42 +1378,42 @@
       <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="1" t="s">
@@ -1359,7 +1479,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.25" style="2" customWidth="1"/>
@@ -1370,8 +1490,8 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" ht="45.75" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5" s="9" customFormat="1" ht="45.75" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1399,6 +1519,9 @@
       <c r="B3" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
@@ -1410,6 +1533,12 @@
       <c r="B4" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="C4" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
@@ -1418,6 +1547,12 @@
       <c r="B5" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="C5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="27">
       <c r="A6" s="2" t="s">
@@ -1426,15 +1561,33 @@
       <c r="B6" s="2" t="s">
         <v>43</v>
       </c>
+      <c r="D6" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="27">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="27">
+      <c r="B7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="108">
       <c r="A8" s="2" t="s">
         <v>47</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1444,6 +1597,12 @@
       <c r="B9" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="C9" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
@@ -1452,6 +1611,12 @@
       <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
+      <c r="C10" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
@@ -1460,13 +1625,64 @@
       <c r="B11" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="5" t="s">
-        <v>79</v>
+      <c r="E11" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="27">
+      <c r="A12" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>80</v>
+        <v>146</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27">
+      <c r="A13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="27">
+      <c r="A14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="27">
+      <c r="A15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -1481,7 +1697,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="43.25" style="2" customWidth="1"/>
@@ -1492,8 +1708,8 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" ht="291" customHeight="1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:5" s="9" customFormat="1" ht="291" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1521,7 +1737,7 @@
     </row>
     <row r="4" spans="1:5" ht="40.5">
       <c r="A4" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>66</v>
@@ -1586,7 +1802,7 @@
         <v>55</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>40</v>
@@ -1600,7 +1816,10 @@
         <v>52</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="81">
@@ -1659,7 +1878,7 @@
         <v>72</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>40</v>
@@ -1673,10 +1892,43 @@
         <v>72</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="27">
+      <c r="A30" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="27">
+      <c r="A31" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -1702,9 +1954,9 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" ht="275.25" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>96</v>
+    <row r="1" spans="1:5" s="9" customFormat="1" ht="275.25" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1726,18 +1978,18 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="40.5">
       <c r="A4" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>40</v>
@@ -1745,65 +1997,92 @@
     </row>
     <row r="5" spans="1:5" ht="54">
       <c r="A5" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="40.5">
       <c r="A6" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="67.5">
       <c r="A7" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="54">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="27">
       <c r="A11" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="27">
       <c r="A12" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="27">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="108">
       <c r="A15" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1814,39 +2093,39 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="27">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="27">
       <c r="A21" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="27">
       <c r="A22" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="27">
       <c r="A23" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1872,9 +2151,9 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" ht="121.5" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>112</v>
+    <row r="1" spans="1:5" s="9" customFormat="1" ht="121.5" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1896,36 +2175,42 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="40.5">
       <c r="A16" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="40.5">
       <c r="A17" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1940,7 +2225,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="45.375" style="2" customWidth="1"/>
@@ -1951,9 +2236,9 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" ht="296.25" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>143</v>
+    <row r="1" spans="1:5" s="9" customFormat="1" ht="296.25" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1974,89 +2259,161 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="8" t="s">
-        <v>121</v>
+      <c r="A4" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="27">
       <c r="A8" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="27">
+      <c r="A12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>146</v>
       </c>
+      <c r="C12" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27">
+      <c r="A13" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="40.5">
+      <c r="A14" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="6" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="54">
+      <c r="A19" s="2" t="s">
+        <v>140</v>
+      </c>
       <c r="B19" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="54">
-      <c r="A20" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="27">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="27">
+      <c r="A25" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="27">
       <c r="A26" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="27">
-      <c r="A27" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2082,9 +2439,9 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="7" customFormat="1" ht="113.25" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>150</v>
+    <row r="1" spans="1:5" s="9" customFormat="1" ht="113.25" customHeight="1">
+      <c r="A1" s="9" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2105,118 +2462,156 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="8" t="s">
-        <v>121</v>
+      <c r="A3" s="6" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="9" t="s">
-        <v>140</v>
+      <c r="A10" s="7" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="27">
       <c r="A11" s="2" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="27">
       <c r="A12" s="2" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="27">
+      <c r="A13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="8" t="s">
-        <v>127</v>
+      <c r="A15" s="6" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="9" t="s">
-        <v>129</v>
+      <c r="A16" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="40.5">
       <c r="A17" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="27">
       <c r="A18" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="27">
       <c r="A30" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="27">
       <c r="A31" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="27">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="27">
       <c r="A37" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -2225,5 +2620,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>